--- a/docs/Anvil/pythonfiles/shakespeare_insultkit.xlsx
+++ b/docs/Anvil/pythonfiles/shakespeare_insultkit.xlsx
@@ -8,20 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://paradevic-my.sharepoint.com/personal/gmccarthy_parade_vic_edu_au/Documents/All DT/microbit for online/PC-app-development/docs/Anvil/pythonfiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="110" documentId="11_7033088E9A73246EBBC32387CB8EC4C83910CD90" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC08C0B1-A514-425F-8E7B-17A8E42FD3FE}"/>
+  <xr:revisionPtr revIDLastSave="115" documentId="11_7033088E9A73246EBBC32387CB8EC4C83910CD90" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27D1FC1E-FD3F-4E02-A92E-E4F06BA8C0AD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="3" r:id="rId1"/>
-    <sheet name="Sheet5" sheetId="7" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="186">
   <si>
     <r>
       <rPr>
@@ -989,332 +988,23 @@
     <t>whey-face</t>
   </si>
   <si>
-    <t>Insult1</t>
-  </si>
-  <si>
-    <t>Insult2</t>
-  </si>
-  <si>
-    <t>Insult3</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>fool</t>
-  </si>
-  <si>
-    <t>moron</t>
-  </si>
-  <si>
-    <t>nitwit</t>
-  </si>
-  <si>
-    <t>twit</t>
-  </si>
-  <si>
-    <t>blockhead</t>
-  </si>
-  <si>
-    <t>bonehead</t>
-  </si>
-  <si>
-    <t>cretin</t>
-  </si>
-  <si>
-    <t>dimwit</t>
-  </si>
-  <si>
-    <t>dork</t>
-  </si>
-  <si>
-    <t>dumbbell</t>
-  </si>
-  <si>
-    <t>dunce</t>
-  </si>
-  <si>
-    <t>ignoramus</t>
-  </si>
-  <si>
-    <t>imbecile</t>
-  </si>
-  <si>
-    <t>muttonhead</t>
-  </si>
-  <si>
-    <t>nincompoop</t>
-  </si>
-  <si>
-    <t>ninny</t>
-  </si>
-  <si>
-    <t>pinhead</t>
-  </si>
-  <si>
-    <t>simpleton</t>
-  </si>
-  <si>
-    <t>clodpoll</t>
-  </si>
-  <si>
-    <t>jerk</t>
-  </si>
-  <si>
-    <t>tomfool</t>
-  </si>
-  <si>
-    <t>awful</t>
-  </si>
-  <si>
-    <t>grisly</t>
-  </si>
-  <si>
-    <t>grotesque</t>
-  </si>
-  <si>
-    <t>hideous</t>
-  </si>
-  <si>
-    <t>horrid</t>
-  </si>
-  <si>
-    <t>unseemly</t>
-  </si>
-  <si>
-    <t>unsightly</t>
-  </si>
-  <si>
-    <t>animal</t>
-  </si>
-  <si>
-    <t>appalling</t>
-  </si>
-  <si>
-    <t>bad-looking</t>
-  </si>
-  <si>
-    <t>beastly</t>
-  </si>
-  <si>
-    <t>deformed</t>
-  </si>
-  <si>
-    <t>disfigured</t>
-  </si>
-  <si>
-    <t>foul</t>
-  </si>
-  <si>
-    <t>frightful</t>
-  </si>
-  <si>
-    <t>gross</t>
-  </si>
-  <si>
-    <t>hard-featured</t>
-  </si>
-  <si>
-    <t>homely</t>
-  </si>
-  <si>
-    <t>ill-favored</t>
-  </si>
-  <si>
-    <t>loathsome</t>
-  </si>
-  <si>
-    <t>misshapen</t>
-  </si>
-  <si>
-    <t>monstrous</t>
-  </si>
-  <si>
-    <t>not much to look at</t>
-  </si>
-  <si>
-    <t>plain</t>
-  </si>
-  <si>
-    <t>repelling</t>
-  </si>
-  <si>
-    <t>repugnant</t>
-  </si>
-  <si>
-    <t>repulsive</t>
-  </si>
-  <si>
-    <t>revolting</t>
-  </si>
-  <si>
-    <t>unbeautiful</t>
-  </si>
-  <si>
-    <t>uncomely</t>
-  </si>
-  <si>
-    <t>uninviting</t>
-  </si>
-  <si>
-    <t>unlovely</t>
-  </si>
-  <si>
-    <t>unprepossessing</t>
-  </si>
-  <si>
-    <t>abusive</t>
-  </si>
-  <si>
-    <t>blunt</t>
-  </si>
-  <si>
-    <t>boorish</t>
-  </si>
-  <si>
-    <t>coarse</t>
-  </si>
-  <si>
-    <t>crude</t>
-  </si>
-  <si>
-    <t>ignorant</t>
-  </si>
-  <si>
-    <t>impolite</t>
-  </si>
-  <si>
-    <t>insulting</t>
-  </si>
-  <si>
-    <t>intrusive</t>
-  </si>
-  <si>
-    <t>obscene</t>
-  </si>
-  <si>
-    <t>surly</t>
-  </si>
-  <si>
-    <t>vulgar</t>
-  </si>
-  <si>
-    <t>uncivil</t>
-  </si>
-  <si>
-    <t>abrupt</t>
-  </si>
-  <si>
-    <t>bad-mannered</t>
-  </si>
-  <si>
-    <t>barbarian</t>
-  </si>
-  <si>
-    <t>barbaric</t>
-  </si>
-  <si>
-    <t>barbarous</t>
-  </si>
-  <si>
-    <t>brusque</t>
-  </si>
-  <si>
-    <t>brutish</t>
-  </si>
-  <si>
-    <t>cheeky</t>
-  </si>
-  <si>
-    <t>churlish</t>
-  </si>
-  <si>
-    <t>crabbed</t>
-  </si>
-  <si>
-    <t>curt</t>
-  </si>
-  <si>
-    <t>discourteous</t>
-  </si>
-  <si>
-    <t>graceless</t>
-  </si>
-  <si>
-    <t>gruff</t>
-  </si>
-  <si>
-    <t>illiterate</t>
-  </si>
-  <si>
-    <t>impertinent</t>
-  </si>
-  <si>
-    <t>impudent</t>
-  </si>
-  <si>
-    <t>inconsiderate</t>
-  </si>
-  <si>
-    <t>insolent</t>
-  </si>
-  <si>
-    <t>loutish</t>
-  </si>
-  <si>
-    <t>low</t>
-  </si>
-  <si>
-    <t>offhand</t>
-  </si>
-  <si>
-    <t>peremptory</t>
-  </si>
-  <si>
-    <t>raw</t>
-  </si>
-  <si>
-    <t>savage</t>
-  </si>
-  <si>
-    <t>scurrilous</t>
-  </si>
-  <si>
-    <t>short</t>
-  </si>
-  <si>
-    <t>uncivilized</t>
-  </si>
-  <si>
-    <t>uncouth</t>
-  </si>
-  <si>
-    <t>uncultured</t>
-  </si>
-  <si>
-    <t>uneducated</t>
-  </si>
-  <si>
-    <t>ungracious</t>
-  </si>
-  <si>
-    <t>unmannerly</t>
-  </si>
-  <si>
-    <t>unpolished</t>
-  </si>
-  <si>
-    <t>unrefined</t>
-  </si>
-  <si>
-    <t>wild</t>
+    <t>term1</t>
+  </si>
+  <si>
+    <t>term2</t>
+  </si>
+  <si>
+    <t>term3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1329,6 +1019,17 @@
       <sz val="9.5"/>
       <name val="Courier New"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Times New Roman"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1351,12 +1052,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1706,14 +1410,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="2" t="s">
         <v>184</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="13.5" x14ac:dyDescent="0.25">
@@ -2388,439 +2092,18 @@
     </row>
     <row r="81" spans="6:8" x14ac:dyDescent="0.2">
       <c r="F81" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G81" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H81" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A21D09B-1222-4B54-8374-C472D04D260E}">
-  <dimension ref="A1:C50"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>207</v>
-      </c>
-      <c r="B1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C1" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>208</v>
-      </c>
-      <c r="B2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>210</v>
-      </c>
-      <c r="B4" t="s">
-        <v>243</v>
-      </c>
-      <c r="C4" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>211</v>
-      </c>
-      <c r="B5" t="s">
-        <v>244</v>
-      </c>
-      <c r="C5" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>212</v>
-      </c>
-      <c r="B6" t="s">
-        <v>245</v>
-      </c>
-      <c r="C6" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>213</v>
-      </c>
-      <c r="B7" t="s">
-        <v>246</v>
-      </c>
-      <c r="C7" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>214</v>
-      </c>
-      <c r="B8" t="s">
-        <v>247</v>
-      </c>
-      <c r="C8" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>215</v>
-      </c>
-      <c r="B9" t="s">
-        <v>248</v>
-      </c>
-      <c r="C9" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>216</v>
-      </c>
-      <c r="B10" t="s">
-        <v>249</v>
-      </c>
-      <c r="C10" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>217</v>
-      </c>
-      <c r="B11" t="s">
-        <v>250</v>
-      </c>
-      <c r="C11" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>218</v>
-      </c>
-      <c r="B12" t="s">
-        <v>251</v>
-      </c>
-      <c r="C12" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>219</v>
-      </c>
-      <c r="B13" t="s">
-        <v>252</v>
-      </c>
-      <c r="C13" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>220</v>
-      </c>
-      <c r="B14" t="s">
-        <v>253</v>
-      </c>
-      <c r="C14" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>221</v>
-      </c>
-      <c r="B15" t="s">
-        <v>254</v>
-      </c>
-      <c r="C15" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>222</v>
-      </c>
-      <c r="B16" t="s">
-        <v>255</v>
-      </c>
-      <c r="C16" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>223</v>
-      </c>
-      <c r="B17" t="s">
-        <v>256</v>
-      </c>
-      <c r="C17" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>224</v>
-      </c>
-      <c r="B18" t="s">
-        <v>257</v>
-      </c>
-      <c r="C18" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>225</v>
-      </c>
-      <c r="B19" t="s">
-        <v>258</v>
-      </c>
-      <c r="C19" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>226</v>
-      </c>
-      <c r="B20" t="s">
-        <v>259</v>
-      </c>
-      <c r="C20" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>227</v>
-      </c>
-      <c r="B21" t="s">
-        <v>260</v>
-      </c>
-      <c r="C21" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>228</v>
-      </c>
-      <c r="B22" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>229</v>
-      </c>
-      <c r="B23" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>230</v>
-      </c>
-      <c r="B24" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>231</v>
-      </c>
-      <c r="B25" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>232</v>
-      </c>
-      <c r="B26" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>233</v>
-      </c>
-      <c r="B27" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>234</v>
-      </c>
-      <c r="B28" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>235</v>
-      </c>
-      <c r="B29" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>236</v>
-      </c>
-      <c r="B30" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>237</v>
-      </c>
-      <c r="B31" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>238</v>
-      </c>
-      <c r="B32" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>239</v>
-      </c>
-      <c r="B33" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B34" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B35" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B36" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B37" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B38" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B39" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B40" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B41" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B42" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B43" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B44" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B45" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B46" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B47" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B48" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B49" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B50" t="s">
-        <v>288</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>